--- a/Sep_2026/Daily Sale/26-09-26/Furqan.xlsx
+++ b/Sep_2026/Daily Sale/26-09-26/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9FF49D-7F54-4DD4-9BC7-95D9F5B4BB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C524D282-E9F1-40F8-AA2D-9FC8D181FE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,6 +47,9 @@
     <sheet name="Sheet3" sheetId="15" state="hidden" r:id="rId37"/>
     <sheet name="Sheet2" sheetId="13" state="hidden" r:id="rId38"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId39"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
   </definedNames>
@@ -55,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="524">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1621,6 +1624,12 @@
   </si>
   <si>
     <t xml:space="preserve">Pak Bakers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer Cash N Carry </t>
+  </si>
+  <si>
+    <t>Address: Zahore Ellahi Road</t>
   </si>
 </sst>
 </file>
@@ -4396,6 +4405,451 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dist Price List (2)"/>
+      <sheetName val="Dist Price List"/>
+      <sheetName val="Cust. Price List"/>
+      <sheetName val="Summary"/>
+      <sheetName val="1"/>
+      <sheetName val="2"/>
+      <sheetName val="3"/>
+      <sheetName val="4"/>
+      <sheetName val="5"/>
+      <sheetName val="6"/>
+      <sheetName val="7"/>
+      <sheetName val="8"/>
+      <sheetName val="9"/>
+      <sheetName val="10"/>
+      <sheetName val="11"/>
+      <sheetName val="12"/>
+      <sheetName val="13"/>
+      <sheetName val="14"/>
+      <sheetName val="15"/>
+      <sheetName val="16"/>
+      <sheetName val="17"/>
+      <sheetName val="18"/>
+      <sheetName val="19"/>
+      <sheetName val="20"/>
+      <sheetName val="21"/>
+      <sheetName val="22"/>
+      <sheetName val="23"/>
+      <sheetName val="24"/>
+      <sheetName val="25"/>
+      <sheetName val="26"/>
+      <sheetName val="27"/>
+      <sheetName val="28"/>
+      <sheetName val="29"/>
+      <sheetName val="30"/>
+      <sheetName val="Customer Invoice (2)"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="6">
+          <cell r="D6" t="str">
+            <v>CCN</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v xml:space="preserve">Meat Masala </v>
+          </cell>
+          <cell r="F6">
+            <v>70</v>
+          </cell>
+          <cell r="G6">
+            <v>40</v>
+          </cell>
+          <cell r="H6">
+            <v>2600</v>
+          </cell>
+          <cell r="I6">
+            <v>65</v>
+          </cell>
+          <cell r="J6">
+            <v>2560.17</v>
+          </cell>
+          <cell r="K6">
+            <v>64.004249999999999</v>
+          </cell>
+          <cell r="L6">
+            <v>2098.5</v>
+          </cell>
+          <cell r="M6">
+            <v>52.462499999999999</v>
+          </cell>
+          <cell r="N6">
+            <v>0.11</v>
+          </cell>
+          <cell r="O6">
+            <v>5.7708750000000002</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="D7" t="str">
+            <v>VTN</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>Lemon Tarka</v>
+          </cell>
+          <cell r="F7">
+            <v>70</v>
+          </cell>
+          <cell r="G7">
+            <v>40</v>
+          </cell>
+          <cell r="H7">
+            <v>2600</v>
+          </cell>
+          <cell r="I7">
+            <v>65</v>
+          </cell>
+          <cell r="J7">
+            <v>2560.17</v>
+          </cell>
+          <cell r="K7">
+            <v>64.004249999999999</v>
+          </cell>
+          <cell r="L7">
+            <v>2098.5</v>
+          </cell>
+          <cell r="M7">
+            <v>52.462499999999999</v>
+          </cell>
+          <cell r="N7">
+            <v>0.11</v>
+          </cell>
+          <cell r="O7">
+            <v>5.7708750000000002</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8" t="str">
+            <v>BCN</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>Chicken Chatkhara</v>
+          </cell>
+          <cell r="F8">
+            <v>70</v>
+          </cell>
+          <cell r="G8">
+            <v>40</v>
+          </cell>
+          <cell r="H8">
+            <v>2600</v>
+          </cell>
+          <cell r="I8">
+            <v>65</v>
+          </cell>
+          <cell r="J8">
+            <v>2560.17</v>
+          </cell>
+          <cell r="K8">
+            <v>64.004249999999999</v>
+          </cell>
+          <cell r="L8">
+            <v>2098.5</v>
+          </cell>
+          <cell r="M8">
+            <v>52.462499999999999</v>
+          </cell>
+          <cell r="N8">
+            <v>0.11</v>
+          </cell>
+          <cell r="O8">
+            <v>5.7708750000000002</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9" t="str">
+            <v>CCNJ</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>Meat Masala (Jumbo)</v>
+          </cell>
+          <cell r="F9">
+            <v>120</v>
+          </cell>
+          <cell r="G9">
+            <v>40</v>
+          </cell>
+          <cell r="H9">
+            <v>3600</v>
+          </cell>
+          <cell r="I9">
+            <v>90</v>
+          </cell>
+          <cell r="J9">
+            <v>3544.8320000000003</v>
+          </cell>
+          <cell r="K9">
+            <v>88.620800000000003</v>
+          </cell>
+          <cell r="L9">
+            <v>2905.6</v>
+          </cell>
+          <cell r="M9">
+            <v>72.64</v>
+          </cell>
+          <cell r="N9">
+            <v>0.11</v>
+          </cell>
+          <cell r="O9">
+            <v>7.9904000000000002</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10" t="str">
+            <v>VTNJ</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>Lemon Tarka (Jumbo)</v>
+          </cell>
+          <cell r="F10">
+            <v>120</v>
+          </cell>
+          <cell r="G10">
+            <v>40</v>
+          </cell>
+          <cell r="H10">
+            <v>3600</v>
+          </cell>
+          <cell r="I10">
+            <v>90</v>
+          </cell>
+          <cell r="J10">
+            <v>3544.8320000000003</v>
+          </cell>
+          <cell r="K10">
+            <v>88.620800000000003</v>
+          </cell>
+          <cell r="L10">
+            <v>2905.6</v>
+          </cell>
+          <cell r="M10">
+            <v>72.64</v>
+          </cell>
+          <cell r="N10">
+            <v>0.11</v>
+          </cell>
+          <cell r="O10">
+            <v>7.9904000000000002</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11" t="str">
+            <v>BCNJ</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>Chicken Chatkhara (Jumbo)</v>
+          </cell>
+          <cell r="F11">
+            <v>120</v>
+          </cell>
+          <cell r="G11">
+            <v>40</v>
+          </cell>
+          <cell r="H11">
+            <v>3600</v>
+          </cell>
+          <cell r="I11">
+            <v>90</v>
+          </cell>
+          <cell r="J11">
+            <v>3544.8320000000003</v>
+          </cell>
+          <cell r="K11">
+            <v>88.620800000000003</v>
+          </cell>
+          <cell r="L11">
+            <v>2905.6</v>
+          </cell>
+          <cell r="M11">
+            <v>72.64</v>
+          </cell>
+          <cell r="N11">
+            <v>0.11</v>
+          </cell>
+          <cell r="O11">
+            <v>7.9904000000000002</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="D12" t="str">
+            <v>CCE</v>
+          </cell>
+          <cell r="E12" t="str">
+            <v>Chicken Chatkhara  (ECO)</v>
+          </cell>
+          <cell r="F12">
+            <v>60</v>
+          </cell>
+          <cell r="G12">
+            <v>40</v>
+          </cell>
+          <cell r="H12">
+            <v>2000</v>
+          </cell>
+          <cell r="I12">
+            <v>50</v>
+          </cell>
+          <cell r="J12">
+            <v>1914.4240000000002</v>
+          </cell>
+          <cell r="K12">
+            <v>47.860600000000005</v>
+          </cell>
+          <cell r="L12">
+            <v>1569.2</v>
+          </cell>
+          <cell r="M12">
+            <v>39.230000000000004</v>
+          </cell>
+          <cell r="N12">
+            <v>0.11</v>
+          </cell>
+          <cell r="O12">
+            <v>4.3153000000000006</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13" t="str">
+            <v>VTE</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>Lemon Tarka (ECO)</v>
+          </cell>
+          <cell r="F13">
+            <v>60</v>
+          </cell>
+          <cell r="G13">
+            <v>40</v>
+          </cell>
+          <cell r="H13">
+            <v>2000</v>
+          </cell>
+          <cell r="I13">
+            <v>50</v>
+          </cell>
+          <cell r="J13">
+            <v>1914.4240000000002</v>
+          </cell>
+          <cell r="K13">
+            <v>47.860600000000005</v>
+          </cell>
+          <cell r="L13">
+            <v>1569.2</v>
+          </cell>
+          <cell r="M13">
+            <v>39.230000000000004</v>
+          </cell>
+          <cell r="N13">
+            <v>0.11</v>
+          </cell>
+          <cell r="O13">
+            <v>4.3153000000000006</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="D14" t="str">
+            <v>BCE</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>Meat Masala (ECO)</v>
+          </cell>
+          <cell r="F14">
+            <v>60</v>
+          </cell>
+          <cell r="G14">
+            <v>40</v>
+          </cell>
+          <cell r="H14">
+            <v>2000</v>
+          </cell>
+          <cell r="I14">
+            <v>50</v>
+          </cell>
+          <cell r="J14">
+            <v>1914.4240000000002</v>
+          </cell>
+          <cell r="K14">
+            <v>47.860600000000005</v>
+          </cell>
+          <cell r="L14">
+            <v>1569.2</v>
+          </cell>
+          <cell r="M14">
+            <v>39.230000000000004</v>
+          </cell>
+          <cell r="N14">
+            <v>0.11</v>
+          </cell>
+          <cell r="O14">
+            <v>4.3153000000000006</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="2">
+          <cell r="H2" t="str">
+            <v>Furqan</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="4">
+          <cell r="N4">
+            <v>46290</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -9993,7 +10447,7 @@
     <col min="22" max="22" width="5.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22 16383:16384" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:22 16383:16384" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="369" t="s">
         <v>91</v>
       </c>
@@ -10039,8 +10493,8 @@
       <c r="L4" s="371"/>
       <c r="M4" s="371"/>
       <c r="N4" s="401">
-        <f>'1'!N4:P4</f>
-        <v>46291</v>
+        <f>'[1]1'!N4:P4</f>
+        <v>46290</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -10068,7 +10522,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -10077,7 +10531,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -10089,7 +10543,7 @@
       <c r="L6" s="371"/>
       <c r="M6" s="371"/>
       <c r="N6" s="400" t="str">
-        <f>Summary!H2</f>
+        <f>[1]Summary!H2</f>
         <v>Furqan</v>
       </c>
       <c r="O6" s="400"/>
@@ -10103,7 +10557,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="371" t="s">
         <v>73</v>
       </c>
@@ -10134,7 +10588,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -10153,7 +10607,7 @@
       <c r="R8" s="85"/>
       <c r="S8" s="267"/>
     </row>
-    <row r="9" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="397" t="s">
         <v>96</v>
       </c>
@@ -10177,7 +10631,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="397" t="s">
         <v>97</v>
       </c>
@@ -10201,7 +10655,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
         <v>480</v>
       </c>
@@ -10373,38 +10827,40 @@
         <v>453</v>
       </c>
       <c r="B16" s="108" t="str">
-        <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A16,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v xml:space="preserve">Meat Masala </v>
       </c>
       <c r="C16" s="105">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,3,0)</f>
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,3,0)</f>
         <v>70</v>
       </c>
       <c r="D16" s="283">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,4,0)</f>
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,4,0)</f>
         <v>40</v>
       </c>
       <c r="E16" s="289">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,6,0)</f>
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,6,0)</f>
         <v>65</v>
       </c>
       <c r="F16" s="290">
-        <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,10,0)</f>
+        <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,10,0)</f>
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="286"/>
-      <c r="H16" s="112"/>
+      <c r="H16" s="112">
+        <v>6</v>
+      </c>
       <c r="I16" s="235">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
+        <v>314.77499999999998</v>
       </c>
       <c r="J16" s="271">
         <f>$I16*S16</f>
-        <v>0</v>
+        <v>31.477499999999999</v>
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>0</v>
+        <v>11.017125</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -10412,23 +10868,25 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>0</v>
+        <v>272.28037499999999</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
-        <v>0</v>
+        <v>59.491525423728788</v>
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>0</v>
+        <v>1.6588595021186439</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="318"/>
+        <v>333.43075992584738</v>
+      </c>
+      <c r="Q16" s="318">
+        <v>14</v>
+      </c>
       <c r="S16" s="269">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T16" s="270">
         <v>3.5000000000000003E-2</v>
@@ -10447,38 +10905,40 @@
         <v>455</v>
       </c>
       <c r="B17" s="109" t="str">
-        <f>VLOOKUP($A17,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A17,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Lemon Tarka</v>
       </c>
       <c r="C17" s="106">
-        <f>VLOOKUP(B17,'Cust. Price List'!E7:P15,2,0)</f>
+        <f>VLOOKUP(B17,'[1]Cust. Price List'!E7:P15,2,0)</f>
         <v>70</v>
       </c>
       <c r="D17" s="284">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,4,0)</f>
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,4,0)</f>
         <v>40</v>
       </c>
       <c r="E17" s="291">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,6,0)</f>
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,6,0)</f>
         <v>65</v>
       </c>
       <c r="F17" s="292">
-        <f>VLOOKUP(A17,'Cust. Price List'!D7:M15,10,0)</f>
+        <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,10,0)</f>
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="287"/>
-      <c r="H17" s="96"/>
+      <c r="H17" s="96">
+        <v>20</v>
+      </c>
       <c r="I17" s="236">
         <f t="shared" ref="I17:I23" si="0">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
+        <v>1049.25</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ref="J17:L24" si="1">$I17*S17</f>
-        <v>0</v>
+        <v>104.92500000000001</v>
       </c>
       <c r="K17" s="128">
         <f>$I17*T17</f>
-        <v>0</v>
+        <v>36.723750000000003</v>
       </c>
       <c r="L17" s="119">
         <f>$I17*U17</f>
@@ -10486,24 +10946,24 @@
       </c>
       <c r="M17" s="230">
         <f t="shared" ref="M17:M24" si="2">I17-SUM(J17:L17)</f>
-        <v>0</v>
+        <v>907.60124999999994</v>
       </c>
       <c r="N17" s="277">
         <f t="shared" ref="N17:N24" si="3">+(G17*D17+H17)*V17</f>
-        <v>0</v>
+        <v>198.30508474576263</v>
       </c>
       <c r="O17" s="239">
         <f t="shared" ref="O17:O24" si="4">(N17+M17)*$O$15</f>
-        <v>0</v>
+        <v>5.5295316737288127</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
-        <v>0</v>
+        <v>1111.4358664194913</v>
       </c>
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
         <f>+S16</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T17" s="270">
         <f>+T16</f>
@@ -10523,38 +10983,40 @@
         <v>457</v>
       </c>
       <c r="B18" s="109" t="str">
-        <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A18,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Chicken Chatkhara</v>
       </c>
       <c r="C18" s="106">
-        <f>VLOOKUP(B18,'Cust. Price List'!E8:P16,2,0)</f>
+        <f>VLOOKUP(B18,'[1]Cust. Price List'!E8:P16,2,0)</f>
         <v>70</v>
       </c>
       <c r="D18" s="284">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,4,0)</f>
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,4,0)</f>
         <v>40</v>
       </c>
       <c r="E18" s="291">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,6,0)</f>
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,6,0)</f>
         <v>65</v>
       </c>
       <c r="F18" s="292">
-        <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,10,0)</f>
+        <f>VLOOKUP(A18,'[1]Cust. Price List'!D8:M16,10,0)</f>
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="287"/>
-      <c r="H18" s="96"/>
+      <c r="H18" s="96">
+        <v>19</v>
+      </c>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>996.78750000000002</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>99.678750000000008</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>34.887562500000001</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -10562,24 +11024,26 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>862.22118750000004</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>188.38983050847449</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.2530550900423725</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="319"/>
+        <v>1055.8640730985169</v>
+      </c>
+      <c r="Q18" s="319">
+        <v>1</v>
+      </c>
       <c r="S18" s="269">
         <f>+S17</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T18" s="270">
         <f>+T17</f>
@@ -10596,38 +11060,40 @@
         <v>459</v>
       </c>
       <c r="B19" s="109" t="str">
-        <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A19,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Meat Masala (Jumbo)</v>
       </c>
       <c r="C19" s="106">
-        <f>VLOOKUP(B19,'Cust. Price List'!E9:P17,2,0)</f>
+        <f>VLOOKUP(B19,'[1]Cust. Price List'!E9:P17,2,0)</f>
         <v>120</v>
       </c>
       <c r="D19" s="284">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,4,0)</f>
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,4,0)</f>
         <v>40</v>
       </c>
       <c r="E19" s="291">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,6,0)</f>
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,6,0)</f>
         <v>90</v>
       </c>
       <c r="F19" s="292">
-        <f>VLOOKUP(A19,'Cust. Price List'!D9:M17,10,0)</f>
+        <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,10,0)</f>
         <v>72.64</v>
       </c>
       <c r="G19" s="287"/>
-      <c r="H19" s="96"/>
+      <c r="H19" s="96">
+        <v>20</v>
+      </c>
       <c r="I19" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>145.28</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -10635,24 +11101,24 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1256.672</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.6562413559322033</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1538.9045125423729</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
         <f>+S18</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T19" s="270">
         <v>3.5000000000000003E-2</v>
@@ -10668,38 +11134,40 @@
         <v>461</v>
       </c>
       <c r="B20" s="109" t="str">
-        <f>VLOOKUP($A20,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A20,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Lemon Tarka (Jumbo)</v>
       </c>
       <c r="C20" s="106">
-        <f>VLOOKUP(B20,'Cust. Price List'!E10:P18,2,0)</f>
+        <f>VLOOKUP(B20,'[1]Cust. Price List'!E10:P18,2,0)</f>
         <v>120</v>
       </c>
       <c r="D20" s="284">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,4,0)</f>
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,4,0)</f>
         <v>40</v>
       </c>
       <c r="E20" s="291">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,6,0)</f>
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,6,0)</f>
         <v>90</v>
       </c>
       <c r="F20" s="292">
-        <f>VLOOKUP(A20,'Cust. Price List'!D10:M18,10,0)</f>
+        <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,10,0)</f>
         <v>72.64</v>
       </c>
       <c r="G20" s="287"/>
-      <c r="H20" s="96"/>
+      <c r="H20" s="96">
+        <v>20</v>
+      </c>
       <c r="I20" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J20" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>145.28</v>
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -10707,28 +11175,28 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1256.672</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.6562413559322033</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1538.9045125423729</v>
       </c>
       <c r="Q20" s="319"/>
       <c r="R20">
         <f>P20/21</f>
-        <v>0</v>
+        <v>73.281167263922526</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T20" s="270">
         <f>+T19</f>
@@ -10745,38 +11213,40 @@
         <v>463</v>
       </c>
       <c r="B21" s="109" t="str">
-        <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A21,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Chicken Chatkhara (Jumbo)</v>
       </c>
       <c r="C21" s="106">
-        <f>VLOOKUP(B21,'Cust. Price List'!E11:P19,2,0)</f>
+        <f>VLOOKUP(B21,'[1]Cust. Price List'!E11:P19,2,0)</f>
         <v>120</v>
       </c>
       <c r="D21" s="284">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,4,0)</f>
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,4,0)</f>
         <v>40</v>
       </c>
       <c r="E21" s="291">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,6,0)</f>
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,6,0)</f>
         <v>90</v>
       </c>
       <c r="F21" s="292">
-        <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,10,0)</f>
+        <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,10,0)</f>
         <v>72.64</v>
       </c>
       <c r="G21" s="287"/>
-      <c r="H21" s="96"/>
+      <c r="H21" s="96">
+        <v>20</v>
+      </c>
       <c r="I21" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1452.8</v>
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>145.28</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -10784,24 +11254,24 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1256.672</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>274.57627118644069</v>
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.6562413559322033</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1538.9045125423729</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
         <f>+S20</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="T21" s="270">
         <f>+T20</f>
@@ -10818,23 +11288,23 @@
         <v>465</v>
       </c>
       <c r="B22" s="109" t="str">
-        <f>VLOOKUP($A22,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A22,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Chicken Chatkhara  (ECO)</v>
       </c>
       <c r="C22" s="106">
-        <f>VLOOKUP(B22,'Cust. Price List'!E12:P20,2,0)</f>
+        <f>VLOOKUP(B22,'[1]Cust. Price List'!E12:P20,2,0)</f>
         <v>60</v>
       </c>
       <c r="D22" s="284">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,4,0)</f>
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,4,0)</f>
         <v>40</v>
       </c>
       <c r="E22" s="291">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,6,0)</f>
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,6,0)</f>
         <v>50</v>
       </c>
       <c r="F22" s="292">
-        <f>VLOOKUP(A22,'Cust. Price List'!D12:M20,10,0)</f>
+        <f>VLOOKUP(A22,'[1]Cust. Price List'!D12:M20,10,0)</f>
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="287"/>
@@ -10891,23 +11361,23 @@
         <v>467</v>
       </c>
       <c r="B23" s="109" t="str">
-        <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A23,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Lemon Tarka (ECO)</v>
       </c>
       <c r="C23" s="106">
-        <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
+        <f>VLOOKUP(B23,'[1]Cust. Price List'!E13:P21,2,0)</f>
         <v>60</v>
       </c>
       <c r="D23" s="284">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,4,0)</f>
         <v>40</v>
       </c>
       <c r="E23" s="291">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,6,0)</f>
         <v>50</v>
       </c>
       <c r="F23" s="292">
-        <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
+        <f>VLOOKUP(A23,'[1]Cust. Price List'!D13:M21,10,0)</f>
         <v>39.230000000000004</v>
       </c>
       <c r="G23" s="287"/>
@@ -10966,23 +11436,23 @@
         <v>469</v>
       </c>
       <c r="B24" s="110" t="str">
-        <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
+        <f>VLOOKUP($A24,'[1]Cust. Price List'!$D$6:$O$14,2,0)</f>
         <v>Meat Masala (ECO)</v>
       </c>
       <c r="C24" s="107">
-        <f>VLOOKUP(B24,'Cust. Price List'!E14:P22,2,0)</f>
+        <f>VLOOKUP(B24,'[1]Cust. Price List'!E14:P22,2,0)</f>
         <v>60</v>
       </c>
       <c r="D24" s="285">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,4,0)</f>
         <v>40</v>
       </c>
       <c r="E24" s="293">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,6,0)</f>
         <v>50</v>
       </c>
       <c r="F24" s="294">
-        <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
+        <f>VLOOKUP(A24,'[1]Cust. Price List'!D14:M22,10,0)</f>
         <v>39.230000000000004</v>
       </c>
       <c r="G24" s="288"/>
@@ -11054,19 +11524,19 @@
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6719.2125000000005</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>0</v>
+        <v>671.92124999999999</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>235.17243750000003</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -11074,23 +11544,23 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5812.1188125000008</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>1269.9152542372879</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>35.410170333686438</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>7117.4442370709739</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -11120,7 +11590,7 @@
       <c r="G27" s="94"/>
       <c r="H27" s="94"/>
     </row>
-    <row r="28" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22 16384:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="375" t="s">
         <v>64</v>
       </c>
@@ -11140,7 +11610,7 @@
       <c r="O28" s="385"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>0</v>
+        <v>6719.2125000000005</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11161,7 +11631,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>0</v>
+        <v>671.92124999999999</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11182,7 +11652,7 @@
       <c r="O30" s="387"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>0</v>
+        <v>235.17243750000003</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11204,7 +11674,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>5812.1188124999999</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11228,7 +11698,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>0</v>
+        <v>1269.9152542372879</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11250,7 +11720,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>7082.0340667372875</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11275,7 +11745,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>35.410170333686438</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11285,7 +11755,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>0</v>
+        <v>7117.4442370709739</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11361,30 +11831,18 @@
     <mergeCell ref="N14:N15"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{00000000-0002-0000-0B00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:P9" xr:uid="{A943F4E2-B601-4F07-AA16-D9E64D65FDFF}">
       <formula1>$XFD$12:$XFD$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{00000000-0002-0000-0B00-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{743C0A99-9D8F-4FD9-A8F8-CDA7C166BD5C}">
       <formula1>$XFC$6:$XFC$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0B00-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{ACD5C030-576B-4674-A834-7A42CE3D097A}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0B00-000003000000}">
-          <x14:formula1>
-            <xm:f>Summary!$B$44:$B$51</xm:f>
-          </x14:formula1>
-          <xm:sqref>N6:P6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -47974,7 +48432,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -48002,7 +48460,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
@@ -54394,19 +54852,19 @@
       </c>
       <c r="H7" s="309">
         <f>+'1'!H16+'2'!H16+'3'!H16+'4'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16+'19'!H16+'20'!H16+'21'!H16+'22'!H16+'23'!H16+'24'!H16+'25'!H16+'26'!H16+'27'!H16+'28'!H16+'29'!H16+'30'!H16</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I7" s="235">
         <f>(G7*D7)*F7+H7*F7</f>
-        <v>1364.0249999999999</v>
+        <v>1678.8</v>
       </c>
       <c r="J7" s="286">
         <f>+'1'!J16+'2'!J16+'3'!J16+'4'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16+'19'!J16+'20'!J16+'21'!J16+'22'!J16+'23'!J16+'24'!J16+'25'!J16+'26'!J16+'27'!J16+'28'!J16+'29'!J16+'30'!J16</f>
-        <v>109.122</v>
+        <v>140.59950000000001</v>
       </c>
       <c r="K7" s="286">
         <f>+'1'!K16+'2'!K16+'3'!K16+'4'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16+'11'!K16+'12'!K16+'13'!K16+'14'!K16+'15'!K16+'16'!K16+'17'!K16+'18'!K16+'19'!K16+'20'!K16+'21'!K16+'22'!K16+'23'!K16+'24'!K16+'25'!K16+'26'!K16+'27'!K16+'28'!K16+'29'!K16+'30'!K16</f>
-        <v>47.740875000000003</v>
+        <v>58.758000000000003</v>
       </c>
       <c r="L7" s="286">
         <f>+'1'!L16+'2'!L16+'3'!L16+'4'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16+'11'!L16+'12'!L16+'13'!L16+'14'!L16+'15'!L16+'16'!L16+'17'!L16+'18'!L16+'19'!L16+'20'!L16+'21'!L16+'22'!L16+'23'!L16+'24'!L16+'25'!L16+'26'!L16+'27'!L16+'28'!L16+'29'!L16+'30'!L16</f>
@@ -54414,23 +54872,23 @@
       </c>
       <c r="M7" s="229">
         <f>I7-SUM(J7:L7)</f>
-        <v>1207.1621249999998</v>
+        <v>1479.4424999999999</v>
       </c>
       <c r="N7" s="286">
         <f>+'1'!N16+'2'!N16+'3'!N16+'4'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16+'11'!N16+'12'!N16+'13'!N16+'14'!N16+'15'!N16+'16'!N16+'17'!N16+'18'!N16+'19'!N16+'20'!N16+'21'!N16+'22'!N16+'23'!N16+'24'!N16+'25'!N16+'26'!N16+'27'!N16+'28'!N16+'29'!N16+'30'!N16</f>
-        <v>257.79661016949143</v>
+        <v>317.2881355932202</v>
       </c>
       <c r="O7" s="286">
         <f>+'1'!O16+'2'!O16+'3'!O16+'4'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16+'11'!O16+'12'!O16+'13'!O16+'14'!O16+'15'!O16+'16'!O16+'17'!O16+'18'!O16+'19'!O16+'20'!O16+'21'!O16+'22'!O16+'23'!O16+'24'!O16+'25'!O16+'26'!O16+'27'!O16+'28'!O16+'29'!O16+'30'!O16</f>
-        <v>7.3247936758474577</v>
+        <v>8.9836531779661009</v>
       </c>
       <c r="P7" s="310">
         <f>M7+N7+O7</f>
-        <v>1472.2835288453389</v>
+        <v>1805.7142887711861</v>
       </c>
       <c r="Q7" s="213">
         <f>+'1'!Q16+'2'!Q16+'3'!Q16+'4'!Q16+'5'!Q16+'6'!Q16+'7'!Q16+'8'!Q16+'9'!Q16+'10'!Q16+'11'!Q16+'12'!Q16+'13'!Q16+'14'!Q16+'15'!Q16+'16'!Q16+'17'!Q16+'18'!Q16+'19'!Q16+'20'!Q16+'21'!Q16+'22'!Q16+'23'!Q16+'24'!Q16+'25'!Q16+'26'!Q16+'27'!Q16+'28'!Q16+'29'!Q16+'30'!Q16</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R7" s="313">
         <v>5</v>
@@ -54477,19 +54935,19 @@
       </c>
       <c r="H8" s="309">
         <f>+'1'!H17+'2'!H17+'3'!H17+'4'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17+'19'!H17+'20'!H17+'21'!H17+'22'!H17+'23'!H17+'24'!H17+'25'!H17+'26'!H17+'27'!H17+'28'!H17+'29'!H17+'30'!H17</f>
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I8" s="236">
         <f t="shared" ref="I8:I14" si="0">(G8*D8)*F8+H8*F8</f>
-        <v>1206.6375</v>
+        <v>2255.8874999999998</v>
       </c>
       <c r="J8" s="286">
         <f>+'1'!J17+'2'!J17+'3'!J17+'4'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17+'19'!J17+'20'!J17+'21'!J17+'22'!J17+'23'!J17+'24'!J17+'25'!J17+'26'!J17+'27'!J17+'28'!J17+'29'!J17+'30'!J17</f>
-        <v>96.530999999999992</v>
+        <v>201.45600000000002</v>
       </c>
       <c r="K8" s="286">
         <f>+'1'!K17+'2'!K17+'3'!K17+'4'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17+'11'!K17+'12'!K17+'13'!K17+'14'!K17+'15'!K17+'16'!K17+'17'!K17+'18'!K17+'19'!K17+'20'!K17+'21'!K17+'22'!K17+'23'!K17+'24'!K17+'25'!K17+'26'!K17+'27'!K17+'28'!K17+'29'!K17+'30'!K17</f>
-        <v>42.232312500000006</v>
+        <v>78.956062500000002</v>
       </c>
       <c r="L8" s="286">
         <f>+'1'!L17+'2'!L17+'3'!L17+'4'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17+'11'!L17+'12'!L17+'13'!L17+'14'!L17+'15'!L17+'16'!L17+'17'!L17+'18'!L17+'19'!L17+'20'!L17+'21'!L17+'22'!L17+'23'!L17+'24'!L17+'25'!L17+'26'!L17+'27'!L17+'28'!L17+'29'!L17+'30'!L17</f>
@@ -54497,19 +54955,19 @@
       </c>
       <c r="M8" s="230">
         <f t="shared" ref="M8:M15" si="1">I8-SUM(J8:L8)</f>
-        <v>1067.8741875000001</v>
+        <v>1975.4754374999998</v>
       </c>
       <c r="N8" s="286">
         <f>+'1'!N17+'2'!N17+'3'!N17+'4'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17+'11'!N17+'12'!N17+'13'!N17+'14'!N17+'15'!N17+'16'!N17+'17'!N17+'18'!N17+'19'!N17+'20'!N17+'21'!N17+'22'!N17+'23'!N17+'24'!N17+'25'!N17+'26'!N17+'27'!N17+'28'!N17+'29'!N17+'30'!N17</f>
-        <v>228.05084745762701</v>
+        <v>426.35593220338967</v>
       </c>
       <c r="O8" s="286">
         <f>+'1'!O17+'2'!O17+'3'!O17+'4'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17+'11'!O17+'12'!O17+'13'!O17+'14'!O17+'15'!O17+'16'!O17+'17'!O17+'18'!O17+'19'!O17+'20'!O17+'21'!O17+'22'!O17+'23'!O17+'24'!O17+'25'!O17+'26'!O17+'27'!O17+'28'!O17+'29'!O17+'30'!O17</f>
-        <v>6.4796251747881346</v>
+        <v>12.009156848516948</v>
       </c>
       <c r="P8" s="311">
         <f t="shared" ref="P8:P15" si="2">M8+N8+O8</f>
-        <v>1302.4046601324153</v>
+        <v>2413.8405265519064</v>
       </c>
       <c r="Q8" s="213">
         <f>+'1'!Q17+'2'!Q17+'3'!Q17+'4'!Q17+'5'!Q17+'6'!Q17+'7'!Q17+'8'!Q17+'9'!Q17+'10'!Q17+'11'!Q17+'12'!Q17+'13'!Q17+'14'!Q17+'15'!Q17+'16'!Q17+'17'!Q17+'18'!Q17+'19'!Q17+'20'!Q17+'21'!Q17+'22'!Q17+'23'!Q17+'24'!Q17+'25'!Q17+'26'!Q17+'27'!Q17+'28'!Q17+'29'!Q17+'30'!Q17</f>
@@ -54560,19 +55018,19 @@
       </c>
       <c r="H9" s="309">
         <f>+'1'!H18+'2'!H18+'3'!H18+'4'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18+'29'!H18+'30'!H18</f>
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="I9" s="236">
         <f t="shared" si="0"/>
-        <v>2098.5</v>
+        <v>3095.2874999999999</v>
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>167.87999999999997</v>
+        <v>267.55874999999997</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>73.447499999999991</v>
+        <v>108.33506249999999</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -54580,23 +55038,23 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>1857.1725000000001</v>
+        <v>2719.3936874999999</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>396.61016949152526</v>
+        <v>584.99999999999977</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>11.268913347457627</v>
+        <v>16.5219684375</v>
       </c>
       <c r="P9" s="311">
         <f t="shared" si="2"/>
-        <v>2265.051582838983</v>
+        <v>3320.9156559375001</v>
       </c>
       <c r="Q9" s="213">
         <f>+'1'!Q18+'2'!Q18+'3'!Q18+'4'!Q18+'5'!Q18+'6'!Q18+'7'!Q18+'8'!Q18+'9'!Q18+'10'!Q18+'11'!Q18+'12'!Q18+'13'!Q18+'14'!Q18+'15'!Q18+'16'!Q18+'17'!Q18+'18'!Q18+'19'!Q18+'20'!Q18+'21'!Q18+'22'!Q18+'23'!Q18+'24'!Q18+'25'!Q18+'26'!Q18+'27'!Q18+'28'!Q18+'29'!Q18+'30'!Q18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="313">
         <v>7</v>
@@ -54640,19 +55098,19 @@
       </c>
       <c r="H10" s="309">
         <f>+'1'!H19+'2'!H19+'3'!H19+'4'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19+'19'!H19+'20'!H19+'21'!H19+'22'!H19+'23'!H19+'24'!H19+'25'!H19+'26'!H19+'27'!H19+'28'!H19+'29'!H19+'30'!H19</f>
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I10" s="236">
         <f t="shared" si="0"/>
-        <v>5302.72</v>
+        <v>6755.52</v>
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>424.21760000000006</v>
+        <v>569.49760000000003</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
-        <v>185.59520000000001</v>
+        <v>236.44320000000002</v>
       </c>
       <c r="L10" s="286">
         <f>+'1'!L19+'2'!L19+'3'!L19+'4'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19+'11'!L19+'12'!L19+'13'!L19+'14'!L19+'15'!L19+'16'!L19+'17'!L19+'18'!L19+'19'!L19+'20'!L19+'21'!L19+'22'!L19+'23'!L19+'24'!L19+'25'!L19+'26'!L19+'27'!L19+'28'!L19+'29'!L19+'30'!L19</f>
@@ -54660,19 +55118,19 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>4692.9072000000006</v>
+        <v>5949.5792000000001</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
-        <v>1002.2033898305084</v>
+        <v>1276.7796610169491</v>
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>28.47555294915254</v>
+        <v>36.131794305084746</v>
       </c>
       <c r="P10" s="311">
         <f t="shared" si="2"/>
-        <v>5723.5861427796608</v>
+        <v>7262.4906553220335</v>
       </c>
       <c r="Q10" s="213">
         <f>+'1'!Q19+'2'!Q19+'3'!Q19+'4'!Q19+'5'!Q19+'6'!Q19+'7'!Q19+'8'!Q19+'9'!Q19+'10'!Q19+'11'!Q19+'12'!Q19+'13'!Q19+'14'!Q19+'15'!Q19+'16'!Q19+'17'!Q19+'18'!Q19+'19'!Q19+'20'!Q19+'21'!Q19+'22'!Q19+'23'!Q19+'24'!Q19+'25'!Q19+'26'!Q19+'27'!Q19+'28'!Q19+'29'!Q19+'30'!Q19</f>
@@ -54683,11 +55141,11 @@
       </c>
       <c r="S10" s="300" t="str">
         <f>+'8'!A6:A6</f>
-        <v>Shop Name</v>
+        <v xml:space="preserve">Peer Cash N Carry </v>
       </c>
       <c r="T10" s="301">
         <f>+'8'!P35</f>
-        <v>0</v>
+        <v>7117.4442370709739</v>
       </c>
     </row>
     <row r="11" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -54720,19 +55178,19 @@
       </c>
       <c r="H11" s="309">
         <f>+'1'!H20+'2'!H20+'3'!H20+'4'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20+'19'!H20+'20'!H20+'21'!H20+'22'!H20+'23'!H20+'24'!H20+'25'!H20+'26'!H20+'27'!H20+'28'!H20+'29'!H20+'30'!H20</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I11" s="236">
         <f t="shared" si="0"/>
-        <v>2905.6</v>
+        <v>4358.3999999999996</v>
       </c>
       <c r="J11" s="286">
         <f>+'1'!J20+'2'!J20+'3'!J20+'4'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20+'19'!J20+'20'!J20+'21'!J20+'22'!J20+'23'!J20+'24'!J20+'25'!J20+'26'!J20+'27'!J20+'28'!J20+'29'!J20+'30'!J20</f>
-        <v>232.44800000000001</v>
+        <v>377.72800000000001</v>
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>101.69600000000001</v>
+        <v>152.54400000000001</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54740,19 +55198,19 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>2571.4560000000001</v>
+        <v>3828.1279999999997</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
-        <v>549.15254237288138</v>
+        <v>823.72881355932213</v>
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>15.603042711864408</v>
+        <v>23.25928406779661</v>
       </c>
       <c r="P11" s="311">
         <f t="shared" si="2"/>
-        <v>3136.2115850847458</v>
+        <v>4675.1160976271176</v>
       </c>
       <c r="Q11" s="213">
         <f>+'1'!Q20+'2'!Q20+'3'!Q20+'4'!Q20+'5'!Q20+'6'!Q20+'7'!Q20+'8'!Q20+'9'!Q20+'10'!Q20+'11'!Q20+'12'!Q20+'13'!Q20+'14'!Q20+'15'!Q20+'16'!Q20+'17'!Q20+'18'!Q20+'19'!Q20+'20'!Q20+'21'!Q20+'22'!Q20+'23'!Q20+'24'!Q20+'25'!Q20+'26'!Q20+'27'!Q20+'28'!Q20+'29'!Q20+'30'!Q20</f>
@@ -54800,19 +55258,19 @@
       </c>
       <c r="H12" s="309">
         <f>+'1'!H21+'2'!H21+'3'!H21+'4'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21+'19'!H21+'20'!H21+'21'!H21+'22'!H21+'23'!H21+'24'!H21+'25'!H21+'26'!H21+'27'!H21+'28'!H21+'29'!H21+'30'!H21</f>
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="I12" s="236">
         <f t="shared" si="0"/>
-        <v>3414.08</v>
+        <v>4866.88</v>
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>273.12640000000005</v>
+        <v>418.40640000000008</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>119.49280000000002</v>
+        <v>170.34080000000003</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54820,19 +55278,19 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>3021.4607999999998</v>
+        <v>4278.1328000000003</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
-        <v>645.25423728813564</v>
+        <v>919.83050847457639</v>
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>18.33357518644068</v>
+        <v>25.989816542372882</v>
       </c>
       <c r="P12" s="311">
         <f t="shared" si="2"/>
-        <v>3685.0486124745762</v>
+        <v>5223.9531250169493</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
@@ -55104,23 +55562,23 @@
       <c r="F16" s="374"/>
       <c r="G16" s="117">
         <f>H16/40</f>
-        <v>6.2249999999999996</v>
+        <v>8.85</v>
       </c>
       <c r="H16" s="113">
         <f t="shared" ref="H16:M16" si="3">SUM(H7:H15)</f>
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>16291.5625</v>
+        <v>23010.775000000001</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>1303.3250000000003</v>
+        <v>1975.2462500000004</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>570.20468749999998</v>
+        <v>805.37712500000009</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -55128,23 +55586,23 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>14418.032812500001</v>
+        <v>20230.151624999999</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>3079.0677966101694</v>
+        <v>4348.9830508474579</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>87.485503045550843</v>
+        <v>122.89567337923729</v>
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>17584.586112155721</v>
+        <v>24702.030349226694</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R16" s="313">
         <v>14</v>
@@ -55227,7 +55685,7 @@
       <c r="O19" s="385"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>16291.5625</v>
+        <v>23010.775000000001</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -55259,7 +55717,7 @@
       <c r="O20" s="387"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>1303.3250000000003</v>
+        <v>1975.2462500000004</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -55291,7 +55749,7 @@
       <c r="O21" s="387"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>570.20468749999998</v>
+        <v>805.37712500000009</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -55324,7 +55782,7 @@
       <c r="O22" s="387"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>14418.0328125</v>
+        <v>20230.151625000002</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -55359,7 +55817,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>3079.0677966101694</v>
+        <v>4348.9830508474579</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -55392,7 +55850,7 @@
       <c r="O24" s="389"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>17497.10060911017</v>
+        <v>24579.134675847461</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -55428,7 +55886,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>87.485503045550843</v>
+        <v>122.89567337923729</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -55449,7 +55907,7 @@
       <c r="O26" s="346"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>17584.586112155721</v>
+        <v>24702.030349226698</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55563,7 +56021,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>17584.586112155721</v>
+        <v>24702.030349226694</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
